--- a/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
@@ -474,16 +474,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -497,16 +500,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -520,16 +526,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -585,7 +594,7 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -608,7 +617,7 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -631,7 +640,7 @@
         <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -690,16 +699,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -713,16 +725,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -736,16 +751,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
   </si>
 </sst>
 </file>
@@ -773,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -803,6 +812,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920051</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>DIEGO IVAN</t>
   </si>
 </sst>
 </file>
@@ -483,10 +492,10 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -495,7 +504,7 @@
         <v>64.52</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -509,10 +518,10 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>14</v>
@@ -521,7 +530,7 @@
         <v>73.68000000000001</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -535,10 +544,10 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>14</v>
@@ -547,7 +556,7 @@
         <v>73.68000000000001</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -600,16 +609,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>61.29</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -623,16 +635,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>68.42</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -646,16 +661,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>68.42</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -708,19 +726,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>64.52</v>
+        <v>61.29</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -734,16 +752,16 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -760,16 +778,16 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>73.68000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -782,7 +800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -814,25 +832,71 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>19330051920056</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920056</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920090</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
   </si>
   <si>
     <t>MARTIN</t>
@@ -800,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -832,22 +841,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920056</v>
+        <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -858,16 +867,16 @@
         <v>19330051920056</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -878,24 +887,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920090</v>
+        <v>19330051920056</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920090</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -76,28 +76,52 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>CANUTO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
+    <t>LEON</t>
   </si>
   <si>
     <t>BAROJAS</t>
   </si>
   <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>MARTIN</t>
+    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>DIEGO IVAN</t>
@@ -809,7 +833,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -841,16 +865,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920073</v>
+        <v>20330051920075</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -864,22 +888,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920056</v>
+        <v>20330051920077</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -890,16 +914,16 @@
         <v>19330051920056</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -910,24 +934,93 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920090</v>
+        <v>19330051920056</v>
       </c>
       <c r="B5" t="s">
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920073</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920080</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920090</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,55 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>ESPINOZA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
     <t>ADRIAN</t>
   </si>
   <si>
     <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
   </si>
 </sst>
 </file>
@@ -762,16 +729,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>61.29</v>
+        <v>74.19</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -833,7 +800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -865,16 +832,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -888,22 +855,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920077</v>
+        <v>19330051920056</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -914,114 +881,22 @@
         <v>19330051920056</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920056</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920073</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920080</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920090</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
+++ b/docentes/Silva Villegas Mario - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -76,22 +76,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
     <t>ESPINOZA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
   </si>
   <si>
     <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
   </si>
 </sst>
 </file>
@@ -755,16 +782,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +827,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -832,16 +859,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920077</v>
+        <v>20330051920069</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -855,22 +882,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920056</v>
+        <v>20330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -878,25 +905,94 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920056</v>
+        <v>19330051920067</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920067</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920074</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920077</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
